--- a/Structure_Data/text.9.14/20260914_08/structure_factor_20260914_08.xlsx
+++ b/Structure_Data/text.9.14/20260914_08/structure_factor_20260914_08.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D381"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,4051 @@
         <v>17.7902233591252</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.393997192382812</v>
+      </c>
+      <c r="C30">
+        <v>0.392967224121094</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.393997192382812</v>
+      </c>
+      <c r="C31">
+        <v>0.392967224121094</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.280693054199219</v>
+      </c>
+      <c r="C32">
+        <v>0.172286987304688</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.109184265136719</v>
+      </c>
+      <c r="C33">
+        <v>0.00987625122070312</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.0699996948242188</v>
+      </c>
+      <c r="C34">
+        <v>0.00647735595703125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.0408210754394531</v>
+      </c>
+      <c r="C35">
+        <v>0.00465011596679688</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.00922393798828125</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.0017242431640625</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.001129150390625</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>32979</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1.56590557627581</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1.35015471058014</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.05</v>
+      </c>
+      <c r="B55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.1</v>
+      </c>
+      <c r="B56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.15</v>
+      </c>
+      <c r="B57">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.2</v>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.25</v>
+      </c>
+      <c r="B59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.3</v>
+      </c>
+      <c r="B60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.35</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.4</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.45</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.5</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.55</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.6</v>
+      </c>
+      <c r="B66">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.7</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.75</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.8</v>
+      </c>
+      <c r="B70">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.85</v>
+      </c>
+      <c r="B71">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.9</v>
+      </c>
+      <c r="B72">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.95</v>
+      </c>
+      <c r="B73">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.5</v>
+      </c>
+      <c r="B75">
+        <v>11041</v>
+      </c>
+      <c r="C75">
+        <v>0.334788804997119</v>
+      </c>
+      <c r="D75">
+        <v>0.334788804997119</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76">
+        <v>7107</v>
+      </c>
+      <c r="C76">
+        <v>0.215500773219321</v>
+      </c>
+      <c r="D76">
+        <v>0.550289578216441</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>1.5</v>
+      </c>
+      <c r="B77">
+        <v>4624</v>
+      </c>
+      <c r="C77">
+        <v>0.140210436944722</v>
+      </c>
+      <c r="D77">
+        <v>0.690500015161163</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>2</v>
+      </c>
+      <c r="B78">
+        <v>3199</v>
+      </c>
+      <c r="C78">
+        <v>0.0970011219260742</v>
+      </c>
+      <c r="D78">
+        <v>0.787501137087237</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>2.5</v>
+      </c>
+      <c r="B79">
+        <v>2133</v>
+      </c>
+      <c r="C79">
+        <v>0.0646775220594924</v>
+      </c>
+      <c r="D79">
+        <v>0.85217865914673</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>3</v>
+      </c>
+      <c r="B80">
+        <v>1458</v>
+      </c>
+      <c r="C80">
+        <v>0.0442099517875011</v>
+      </c>
+      <c r="D80">
+        <v>0.896388610934231</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>3.5</v>
+      </c>
+      <c r="B81">
+        <v>1036</v>
+      </c>
+      <c r="C81">
+        <v>0.0314139300767155</v>
+      </c>
+      <c r="D81">
+        <v>0.927802541010946</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>4</v>
+      </c>
+      <c r="B82">
+        <v>707</v>
+      </c>
+      <c r="C82">
+        <v>0.0214378847145153</v>
+      </c>
+      <c r="D82">
+        <v>0.949240425725462</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>4.5</v>
+      </c>
+      <c r="B83">
+        <v>511</v>
+      </c>
+      <c r="C83">
+        <v>0.0154947087540556</v>
+      </c>
+      <c r="D83">
+        <v>0.964735134479517</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>5</v>
+      </c>
+      <c r="B84">
+        <v>329</v>
+      </c>
+      <c r="C84">
+        <v>0.00997604536220019</v>
+      </c>
+      <c r="D84">
+        <v>0.974711179841717</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>5.5</v>
+      </c>
+      <c r="B85">
+        <v>242</v>
+      </c>
+      <c r="C85">
+        <v>0.00733800297158798</v>
+      </c>
+      <c r="D85">
+        <v>0.982049182813305</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>171</v>
+      </c>
+      <c r="C86">
+        <v>0.00518511780223779</v>
+      </c>
+      <c r="D86">
+        <v>0.987234300615543</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>6.5</v>
+      </c>
+      <c r="B87">
+        <v>134</v>
+      </c>
+      <c r="C87">
+        <v>0.00406319172806938</v>
+      </c>
+      <c r="D87">
+        <v>0.991297492343613</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>7</v>
+      </c>
+      <c r="B88">
+        <v>92</v>
+      </c>
+      <c r="C88">
+        <v>0.00278965402225659</v>
+      </c>
+      <c r="D88">
+        <v>0.994087146365869</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>7.5</v>
+      </c>
+      <c r="B89">
+        <v>52</v>
+      </c>
+      <c r="C89">
+        <v>0.00157676096910155</v>
+      </c>
+      <c r="D89">
+        <v>0.995663907334971</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>8</v>
+      </c>
+      <c r="B90">
+        <v>40</v>
+      </c>
+      <c r="C90">
+        <v>0.00121289305315504</v>
+      </c>
+      <c r="D90">
+        <v>0.996876800388126</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>8.5</v>
+      </c>
+      <c r="B91">
+        <v>31</v>
+      </c>
+      <c r="C91">
+        <v>0.000939992116195154</v>
+      </c>
+      <c r="D91">
+        <v>0.997816792504321</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>9</v>
+      </c>
+      <c r="B92">
+        <v>19</v>
+      </c>
+      <c r="C92">
+        <v>0.000576124200248643</v>
+      </c>
+      <c r="D92">
+        <v>0.99839291670457</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>9.5</v>
+      </c>
+      <c r="B93">
+        <v>20</v>
+      </c>
+      <c r="C93">
+        <v>0.000606446526577519</v>
+      </c>
+      <c r="D93">
+        <v>0.998999363231147</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>10</v>
+      </c>
+      <c r="B94">
+        <v>7</v>
+      </c>
+      <c r="C94">
+        <v>0.000212256284302132</v>
+      </c>
+      <c r="D94">
+        <v>0.999211619515449</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>10.5</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95">
+        <v>0.000242578610631008</v>
+      </c>
+      <c r="D95">
+        <v>0.99945419812608</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>11</v>
+      </c>
+      <c r="B96">
+        <v>8</v>
+      </c>
+      <c r="C96">
+        <v>0.000242578610631008</v>
+      </c>
+      <c r="D96">
+        <v>0.999696776736711</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>11.5</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>3.0322326328876e-05</v>
+      </c>
+      <c r="D97">
+        <v>0.99972709906304</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>12</v>
+      </c>
+      <c r="B98">
+        <v>4</v>
+      </c>
+      <c r="C98">
+        <v>0.000121289305315504</v>
+      </c>
+      <c r="D98">
+        <v>0.999848388368356</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>12.5</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>3.0322326328876e-05</v>
+      </c>
+      <c r="D99">
+        <v>0.999878710694684</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>13</v>
+      </c>
+      <c r="B100">
+        <v>2</v>
+      </c>
+      <c r="C100">
+        <v>6.06446526577519e-05</v>
+      </c>
+      <c r="D100">
+        <v>0.999939355347342</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>14</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>3.0322326328876e-05</v>
+      </c>
+      <c r="D101">
+        <v>0.999969677673671</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>15</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>3.0322326328876e-05</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>158860</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.724473315923556</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.479608999558568</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>0.05</v>
+      </c>
+      <c r="B117">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>0.1</v>
+      </c>
+      <c r="B118">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>0.15</v>
+      </c>
+      <c r="B119">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>0.2</v>
+      </c>
+      <c r="B120">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>0.25</v>
+      </c>
+      <c r="B121">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0.3</v>
+      </c>
+      <c r="B122">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>0.35</v>
+      </c>
+      <c r="B123">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>0.4</v>
+      </c>
+      <c r="B124">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>0.45</v>
+      </c>
+      <c r="B125">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>0.5</v>
+      </c>
+      <c r="B126">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>0.55</v>
+      </c>
+      <c r="B127">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>0.6</v>
+      </c>
+      <c r="B128">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>0.65</v>
+      </c>
+      <c r="B129">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>0.7</v>
+      </c>
+      <c r="B130">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>0.75</v>
+      </c>
+      <c r="B131">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>0.8</v>
+      </c>
+      <c r="B132">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>0.85</v>
+      </c>
+      <c r="B133">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>0.9</v>
+      </c>
+      <c r="B134">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>0.95</v>
+      </c>
+      <c r="B135">
+        <v>1.6583123951777</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>0.5</v>
+      </c>
+      <c r="B137">
+        <v>97829</v>
+      </c>
+      <c r="C137">
+        <v>0.615818960090646</v>
+      </c>
+      <c r="D137">
+        <v>0.615818960090646</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B138">
+        <v>31421</v>
+      </c>
+      <c r="C138">
+        <v>0.197790507364975</v>
+      </c>
+      <c r="D138">
+        <v>0.813609467455621</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B139">
+        <v>6601</v>
+      </c>
+      <c r="C139">
+        <v>0.041552310210248</v>
+      </c>
+      <c r="D139">
+        <v>0.855161777665869</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>1</v>
+      </c>
+      <c r="B140">
+        <v>3258</v>
+      </c>
+      <c r="C140">
+        <v>0.0205086239456125</v>
+      </c>
+      <c r="D140">
+        <v>0.875670401611482</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B141">
+        <v>4440</v>
+      </c>
+      <c r="C141">
+        <v>0.0279491376054388</v>
+      </c>
+      <c r="D141">
+        <v>0.903619539216921</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B142">
+        <v>2289</v>
+      </c>
+      <c r="C142">
+        <v>0.0144089135087498</v>
+      </c>
+      <c r="D142">
+        <v>0.91802845272567</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B143">
+        <v>938</v>
+      </c>
+      <c r="C143">
+        <v>0.00590457006168954</v>
+      </c>
+      <c r="D143">
+        <v>0.92393302278736</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>1.5</v>
+      </c>
+      <c r="B144">
+        <v>2105</v>
+      </c>
+      <c r="C144">
+        <v>0.0132506609593353</v>
+      </c>
+      <c r="D144">
+        <v>0.937183683746695</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B145">
+        <v>1199</v>
+      </c>
+      <c r="C145">
+        <v>0.00754752612363087</v>
+      </c>
+      <c r="D145">
+        <v>0.944731209870326</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B146">
+        <v>838</v>
+      </c>
+      <c r="C146">
+        <v>0.00527508498048596</v>
+      </c>
+      <c r="D146">
+        <v>0.950006294850812</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B147">
+        <v>256</v>
+      </c>
+      <c r="C147">
+        <v>0.00161148180788115</v>
+      </c>
+      <c r="D147">
+        <v>0.951617776658693</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B148">
+        <v>646</v>
+      </c>
+      <c r="C148">
+        <v>0.0040664736245751</v>
+      </c>
+      <c r="D148">
+        <v>0.955684250283268</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B149">
+        <v>974</v>
+      </c>
+      <c r="C149">
+        <v>0.00613118469092283</v>
+      </c>
+      <c r="D149">
+        <v>0.961815434974191</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2</v>
+      </c>
+      <c r="B150">
+        <v>306</v>
+      </c>
+      <c r="C150">
+        <v>0.00192622434848294</v>
+      </c>
+      <c r="D150">
+        <v>0.963741659322674</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B151">
+        <v>863</v>
+      </c>
+      <c r="C151">
+        <v>0.00543245625078686</v>
+      </c>
+      <c r="D151">
+        <v>0.969174115573461</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B152">
+        <v>440</v>
+      </c>
+      <c r="C152">
+        <v>0.00276973435729573</v>
+      </c>
+      <c r="D152">
+        <v>0.971943849930757</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B153">
+        <v>240</v>
+      </c>
+      <c r="C153">
+        <v>0.00151076419488858</v>
+      </c>
+      <c r="D153">
+        <v>0.973454614125645</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B154">
+        <v>223</v>
+      </c>
+      <c r="C154">
+        <v>0.00140375173108397</v>
+      </c>
+      <c r="D154">
+        <v>0.974858365856729</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B155">
+        <v>378</v>
+      </c>
+      <c r="C155">
+        <v>0.00237945360694952</v>
+      </c>
+      <c r="D155">
+        <v>0.977237819463679</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B156">
+        <v>177</v>
+      </c>
+      <c r="C156">
+        <v>0.00111418859373033</v>
+      </c>
+      <c r="D156">
+        <v>0.978352008057409</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B157">
+        <v>162</v>
+      </c>
+      <c r="C157">
+        <v>0.00101976583154979</v>
+      </c>
+      <c r="D157">
+        <v>0.979371773888959</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>2.5</v>
+      </c>
+      <c r="B158">
+        <v>333</v>
+      </c>
+      <c r="C158">
+        <v>0.00209618532040791</v>
+      </c>
+      <c r="D158">
+        <v>0.981467959209367</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B159">
+        <v>440</v>
+      </c>
+      <c r="C159">
+        <v>0.00276973435729573</v>
+      </c>
+      <c r="D159">
+        <v>0.984237693566662</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B160">
+        <v>157</v>
+      </c>
+      <c r="C160">
+        <v>0.000988291577489614</v>
+      </c>
+      <c r="D160">
+        <v>0.985225985144152</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B161">
+        <v>273</v>
+      </c>
+      <c r="C161">
+        <v>0.00171849427168576</v>
+      </c>
+      <c r="D161">
+        <v>0.986944479415838</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B162">
+        <v>133</v>
+      </c>
+      <c r="C162">
+        <v>0.000837215158000755</v>
+      </c>
+      <c r="D162">
+        <v>0.987781694573839</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B163">
+        <v>34</v>
+      </c>
+      <c r="C163">
+        <v>0.000214024927609216</v>
+      </c>
+      <c r="D163">
+        <v>0.987995719501448</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B164">
+        <v>132</v>
+      </c>
+      <c r="C164">
+        <v>0.00083092030718872</v>
+      </c>
+      <c r="D164">
+        <v>0.988826639808636</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B165">
+        <v>114</v>
+      </c>
+      <c r="C165">
+        <v>0.000717612992572076</v>
+      </c>
+      <c r="D165">
+        <v>0.989544252801209</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B166">
+        <v>96</v>
+      </c>
+      <c r="C166">
+        <v>0.000604305677955432</v>
+      </c>
+      <c r="D166">
+        <v>0.990148558479164</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>3</v>
+      </c>
+      <c r="B167">
+        <v>163</v>
+      </c>
+      <c r="C167">
+        <v>0.00102606068236183</v>
+      </c>
+      <c r="D167">
+        <v>0.991174619161526</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B168">
+        <v>116</v>
+      </c>
+      <c r="C168">
+        <v>0.000730202694196148</v>
+      </c>
+      <c r="D168">
+        <v>0.991904821855722</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B169">
+        <v>143</v>
+      </c>
+      <c r="C169">
+        <v>0.000900163666121113</v>
+      </c>
+      <c r="D169">
+        <v>0.992804985521843</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B170">
+        <v>40</v>
+      </c>
+      <c r="C170">
+        <v>0.00025179403248143</v>
+      </c>
+      <c r="D170">
+        <v>0.993056779554325</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B171">
+        <v>128</v>
+      </c>
+      <c r="C171">
+        <v>0.000805740903940577</v>
+      </c>
+      <c r="D171">
+        <v>0.993862520458265</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B172">
+        <v>44</v>
+      </c>
+      <c r="C172">
+        <v>0.000276973435729573</v>
+      </c>
+      <c r="D172">
+        <v>0.994139493893995</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B173">
+        <v>41</v>
+      </c>
+      <c r="C173">
+        <v>0.000258088883293466</v>
+      </c>
+      <c r="D173">
+        <v>0.994397582777288</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B174">
+        <v>25</v>
+      </c>
+      <c r="C174">
+        <v>0.000157371270300894</v>
+      </c>
+      <c r="D174">
+        <v>0.994554954047589</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B175">
+        <v>64</v>
+      </c>
+      <c r="C175">
+        <v>0.000402870451970288</v>
+      </c>
+      <c r="D175">
+        <v>0.994957824499559</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B176">
+        <v>40</v>
+      </c>
+      <c r="C176">
+        <v>0.00025179403248143</v>
+      </c>
+      <c r="D176">
+        <v>0.995209618532041</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B177">
+        <v>10</v>
+      </c>
+      <c r="C177">
+        <v>6.29485081203576e-05</v>
+      </c>
+      <c r="D177">
+        <v>0.995272567040161</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>3.5</v>
+      </c>
+      <c r="B178">
+        <v>120</v>
+      </c>
+      <c r="C178">
+        <v>0.000755382097444291</v>
+      </c>
+      <c r="D178">
+        <v>0.996027949137605</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B179">
+        <v>117</v>
+      </c>
+      <c r="C179">
+        <v>0.000736497545008183</v>
+      </c>
+      <c r="D179">
+        <v>0.996764446682614</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B180">
+        <v>36</v>
+      </c>
+      <c r="C180">
+        <v>0.000226614629233287</v>
+      </c>
+      <c r="D180">
+        <v>0.996991061311847</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>3.60555127546399</v>
+      </c>
+      <c r="B181">
+        <v>8</v>
+      </c>
+      <c r="C181">
+        <v>5.0358806496286e-05</v>
+      </c>
+      <c r="D181">
+        <v>0.997041420118343</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B182">
+        <v>41</v>
+      </c>
+      <c r="C182">
+        <v>0.000258088883293466</v>
+      </c>
+      <c r="D182">
+        <v>0.997299509001637</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B183">
+        <v>45</v>
+      </c>
+      <c r="C183">
+        <v>0.000283268286541609</v>
+      </c>
+      <c r="D183">
+        <v>0.997582777288178</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B184">
+        <v>18</v>
+      </c>
+      <c r="C184">
+        <v>0.000113307314616644</v>
+      </c>
+      <c r="D184">
+        <v>0.997696084602795</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>3.77491721763537</v>
+      </c>
+      <c r="B185">
+        <v>23</v>
+      </c>
+      <c r="C185">
+        <v>0.000144781568676822</v>
+      </c>
+      <c r="D185">
+        <v>0.997840866171472</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>3.80788655293195</v>
+      </c>
+      <c r="B186">
+        <v>7</v>
+      </c>
+      <c r="C186">
+        <v>4.40639556842503e-05</v>
+      </c>
+      <c r="D186">
+        <v>0.997884930127156</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>3.8405728739343</v>
+      </c>
+      <c r="B187">
+        <v>25</v>
+      </c>
+      <c r="C187">
+        <v>0.000157371270300894</v>
+      </c>
+      <c r="D187">
+        <v>0.998042301397457</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>3.90512483795333</v>
+      </c>
+      <c r="B188">
+        <v>25</v>
+      </c>
+      <c r="C188">
+        <v>0.000157371270300894</v>
+      </c>
+      <c r="D188">
+        <v>0.998199672667758</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>3.93700393700591</v>
+      </c>
+      <c r="B189">
+        <v>25</v>
+      </c>
+      <c r="C189">
+        <v>0.000157371270300894</v>
+      </c>
+      <c r="D189">
+        <v>0.998357043938059</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>4</v>
+      </c>
+      <c r="B190">
+        <v>35</v>
+      </c>
+      <c r="C190">
+        <v>0.000220319778421251</v>
+      </c>
+      <c r="D190">
+        <v>0.99857736371648</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>4.03112887414927</v>
+      </c>
+      <c r="B191">
+        <v>56</v>
+      </c>
+      <c r="C191">
+        <v>0.000352511645474002</v>
+      </c>
+      <c r="D191">
+        <v>0.998929875361954</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>4.06201920231798</v>
+      </c>
+      <c r="B192">
+        <v>32</v>
+      </c>
+      <c r="C192">
+        <v>0.000201435225985144</v>
+      </c>
+      <c r="D192">
+        <v>0.999131310587939</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>4.09267638593623</v>
+      </c>
+      <c r="B193">
+        <v>6</v>
+      </c>
+      <c r="C193">
+        <v>3.77691048722145e-05</v>
+      </c>
+      <c r="D193">
+        <v>0.999169079692811</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>4.12310562561766</v>
+      </c>
+      <c r="B194">
+        <v>17</v>
+      </c>
+      <c r="C194">
+        <v>0.000107012463804608</v>
+      </c>
+      <c r="D194">
+        <v>0.999276092156616</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>4.15331193145904</v>
+      </c>
+      <c r="B195">
+        <v>14</v>
+      </c>
+      <c r="C195">
+        <v>8.81279113685006e-05</v>
+      </c>
+      <c r="D195">
+        <v>0.999364220067984</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>4.18330013267038</v>
+      </c>
+      <c r="B196">
+        <v>7</v>
+      </c>
+      <c r="C196">
+        <v>4.40639556842503e-05</v>
+      </c>
+      <c r="D196">
+        <v>0.999408284023669</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>4.24264068711928</v>
+      </c>
+      <c r="B197">
+        <v>7</v>
+      </c>
+      <c r="C197">
+        <v>4.40639556842503e-05</v>
+      </c>
+      <c r="D197">
+        <v>0.999452347979353</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>4.27200187265877</v>
+      </c>
+      <c r="B198">
+        <v>5</v>
+      </c>
+      <c r="C198">
+        <v>3.14742540601788e-05</v>
+      </c>
+      <c r="D198">
+        <v>0.999483822233413</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>4.30116263352131</v>
+      </c>
+      <c r="B199">
+        <v>11</v>
+      </c>
+      <c r="C199">
+        <v>6.92433589323933e-05</v>
+      </c>
+      <c r="D199">
+        <v>0.999553065592345</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>4.33012701892219</v>
+      </c>
+      <c r="B200">
+        <v>6</v>
+      </c>
+      <c r="C200">
+        <v>3.77691048722145e-05</v>
+      </c>
+      <c r="D200">
+        <v>0.999590834697218</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>4.35889894354067</v>
+      </c>
+      <c r="B201">
+        <v>2</v>
+      </c>
+      <c r="C201">
+        <v>1.25897016240715e-05</v>
+      </c>
+      <c r="D201">
+        <v>0.999603424398842</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>4.38748219369606</v>
+      </c>
+      <c r="B202">
+        <v>9</v>
+      </c>
+      <c r="C202">
+        <v>5.66536573083218e-05</v>
+      </c>
+      <c r="D202">
+        <v>0.99966007805615</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>4.41588043316392</v>
+      </c>
+      <c r="B203">
+        <v>3</v>
+      </c>
+      <c r="C203">
+        <v>1.88845524361073e-05</v>
+      </c>
+      <c r="D203">
+        <v>0.999678962608586</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>4.5</v>
+      </c>
+      <c r="B204">
+        <v>13</v>
+      </c>
+      <c r="C204">
+        <v>8.18330605564648e-05</v>
+      </c>
+      <c r="D204">
+        <v>0.999760795669143</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>4.52769256906871</v>
+      </c>
+      <c r="B205">
+        <v>18</v>
+      </c>
+      <c r="C205">
+        <v>0.000113307314616644</v>
+      </c>
+      <c r="D205">
+        <v>0.999874102983759</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>4.55521678957215</v>
+      </c>
+      <c r="B206">
+        <v>9</v>
+      </c>
+      <c r="C206">
+        <v>5.66536573083218e-05</v>
+      </c>
+      <c r="D206">
+        <v>0.999930756641068</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>4.58257569495584</v>
+      </c>
+      <c r="B207">
+        <v>2</v>
+      </c>
+      <c r="C207">
+        <v>1.25897016240715e-05</v>
+      </c>
+      <c r="D207">
+        <v>0.999943346342692</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>4.60977222864644</v>
+      </c>
+      <c r="B208">
+        <v>4</v>
+      </c>
+      <c r="C208">
+        <v>2.5179403248143e-05</v>
+      </c>
+      <c r="D208">
+        <v>0.99996852574594</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>4.63680924774785</v>
+      </c>
+      <c r="B209">
+        <v>1</v>
+      </c>
+      <c r="C209">
+        <v>6.29485081203575e-06</v>
+      </c>
+      <c r="D209">
+        <v>0.999974820596752</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>4.7169905660283</v>
+      </c>
+      <c r="B210">
+        <v>3</v>
+      </c>
+      <c r="C210">
+        <v>1.88845524361073e-05</v>
+      </c>
+      <c r="D210">
+        <v>0.999993705149188</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>4.89897948556636</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+      <c r="C211">
+        <v>6.29485081203575e-06</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212"/>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B217">
+        <v>0.393997192382812</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B218">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>0</v>
+      </c>
+      <c r="B223">
+        <v>0.393997192382812</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>0.5</v>
+      </c>
+      <c r="B224">
+        <v>0.270201365152995</v>
+      </c>
+      <c r="C224">
+        <v>6</v>
+      </c>
+      <c r="D224">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>1</v>
+      </c>
+      <c r="B225">
+        <v>0.220843095045823</v>
+      </c>
+      <c r="C225">
+        <v>26</v>
+      </c>
+      <c r="D225">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>1.5</v>
+      </c>
+      <c r="B226">
+        <v>0.181790415445964</v>
+      </c>
+      <c r="C226">
+        <v>90</v>
+      </c>
+      <c r="D226">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>2</v>
+      </c>
+      <c r="B227">
+        <v>0.173283989749738</v>
+      </c>
+      <c r="C227">
+        <v>134</v>
+      </c>
+      <c r="D227">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>2.5</v>
+      </c>
+      <c r="B228">
+        <v>0.176412035328473</v>
+      </c>
+      <c r="C228">
+        <v>258</v>
+      </c>
+      <c r="D228">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>3</v>
+      </c>
+      <c r="B229">
+        <v>0.175556573635194</v>
+      </c>
+      <c r="C229">
+        <v>410</v>
+      </c>
+      <c r="D229">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>3.5</v>
+      </c>
+      <c r="B230">
+        <v>0.173930982829106</v>
+      </c>
+      <c r="C230">
+        <v>494</v>
+      </c>
+      <c r="D230">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>4</v>
+      </c>
+      <c r="B231">
+        <v>0.172869231735451</v>
+      </c>
+      <c r="C231">
+        <v>690</v>
+      </c>
+      <c r="D231">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>4.5</v>
+      </c>
+      <c r="B232">
+        <v>0.171787951939319</v>
+      </c>
+      <c r="C232">
+        <v>962</v>
+      </c>
+      <c r="D232">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>5</v>
+      </c>
+      <c r="B233">
+        <v>0.170660314229885</v>
+      </c>
+      <c r="C233">
+        <v>1098</v>
+      </c>
+      <c r="D233">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>5.5</v>
+      </c>
+      <c r="B234">
+        <v>0.16962192475711</v>
+      </c>
+      <c r="C234">
+        <v>1406</v>
+      </c>
+      <c r="D234">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>6</v>
+      </c>
+      <c r="B235">
+        <v>0.168566269868529</v>
+      </c>
+      <c r="C235">
+        <v>1578</v>
+      </c>
+      <c r="D235">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>6.5</v>
+      </c>
+      <c r="B236">
+        <v>0.167608773389349</v>
+      </c>
+      <c r="C236">
+        <v>2018</v>
+      </c>
+      <c r="D236">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>7</v>
+      </c>
+      <c r="B237">
+        <v>0.166593028784409</v>
+      </c>
+      <c r="C237">
+        <v>2342</v>
+      </c>
+      <c r="D237">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>7.5</v>
+      </c>
+      <c r="B238">
+        <v>0.165606102621184</v>
+      </c>
+      <c r="C238">
+        <v>2634</v>
+      </c>
+      <c r="D238">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>8</v>
+      </c>
+      <c r="B239">
+        <v>0.164654043672842</v>
+      </c>
+      <c r="C239">
+        <v>2930</v>
+      </c>
+      <c r="D239">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>8.5</v>
+      </c>
+      <c r="B240">
+        <v>0.163719309560696</v>
+      </c>
+      <c r="C240">
+        <v>3402</v>
+      </c>
+      <c r="D240">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>9</v>
+      </c>
+      <c r="B241">
+        <v>0.162848922954915</v>
+      </c>
+      <c r="C241">
+        <v>3926</v>
+      </c>
+      <c r="D241">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>9.5</v>
+      </c>
+      <c r="B242">
+        <v>0.161993973701144</v>
+      </c>
+      <c r="C242">
+        <v>4266</v>
+      </c>
+      <c r="D242">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>10</v>
+      </c>
+      <c r="B243">
+        <v>0.161220074708064</v>
+      </c>
+      <c r="C243">
+        <v>4730</v>
+      </c>
+      <c r="D243">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>10.5</v>
+      </c>
+      <c r="B244">
+        <v>0.160445081430425</v>
+      </c>
+      <c r="C244">
+        <v>5510</v>
+      </c>
+      <c r="D244">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>11</v>
+      </c>
+      <c r="B245">
+        <v>0.159686548424384</v>
+      </c>
+      <c r="C245">
+        <v>5562</v>
+      </c>
+      <c r="D245">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>11.5</v>
+      </c>
+      <c r="B246">
+        <v>0.158904349673743</v>
+      </c>
+      <c r="C246">
+        <v>6410</v>
+      </c>
+      <c r="D246">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>12</v>
+      </c>
+      <c r="B247">
+        <v>0.158196585677069</v>
+      </c>
+      <c r="C247">
+        <v>6894</v>
+      </c>
+      <c r="D247">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>12.5</v>
+      </c>
+      <c r="B248">
+        <v>0.157570308995979</v>
+      </c>
+      <c r="C248">
+        <v>7490</v>
+      </c>
+      <c r="D248">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>13</v>
+      </c>
+      <c r="B249">
+        <v>0.156987259306553</v>
+      </c>
+      <c r="C249">
+        <v>8258</v>
+      </c>
+      <c r="D249">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>13.5</v>
+      </c>
+      <c r="B250">
+        <v>0.156447750105973</v>
+      </c>
+      <c r="C250">
+        <v>8994</v>
+      </c>
+      <c r="D250">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>14</v>
+      </c>
+      <c r="B251">
+        <v>0.155927853137034</v>
+      </c>
+      <c r="C251">
+        <v>9446</v>
+      </c>
+      <c r="D251">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>14.5</v>
+      </c>
+      <c r="B252">
+        <v>0.155418320298553</v>
+      </c>
+      <c r="C252">
+        <v>9978</v>
+      </c>
+      <c r="D252">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>15</v>
+      </c>
+      <c r="B253">
+        <v>0.154904215355967</v>
+      </c>
+      <c r="C253">
+        <v>11138</v>
+      </c>
+      <c r="D253">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>15.5</v>
+      </c>
+      <c r="B254">
+        <v>0.154482536309229</v>
+      </c>
+      <c r="C254">
+        <v>11406</v>
+      </c>
+      <c r="D254">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>16</v>
+      </c>
+      <c r="B255">
+        <v>0.154072695783308</v>
+      </c>
+      <c r="C255">
+        <v>12575</v>
+      </c>
+      <c r="D255">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>16.5</v>
+      </c>
+      <c r="B256">
+        <v>0.153645448340277</v>
+      </c>
+      <c r="C256">
+        <v>12848</v>
+      </c>
+      <c r="D256">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>17</v>
+      </c>
+      <c r="B257">
+        <v>0.153136769890983</v>
+      </c>
+      <c r="C257">
+        <v>12060</v>
+      </c>
+      <c r="D257">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>17.5</v>
+      </c>
+      <c r="B258">
+        <v>0.152696250132164</v>
+      </c>
+      <c r="C258">
+        <v>11804</v>
+      </c>
+      <c r="D258">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>18</v>
+      </c>
+      <c r="B259">
+        <v>0.152236441208473</v>
+      </c>
+      <c r="C259">
+        <v>11016</v>
+      </c>
+      <c r="D259">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>18.5</v>
+      </c>
+      <c r="B260">
+        <v>0.151820016308366</v>
+      </c>
+      <c r="C260">
+        <v>10700</v>
+      </c>
+      <c r="D260">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>19</v>
+      </c>
+      <c r="B261">
+        <v>0.151476637561481</v>
+      </c>
+      <c r="C261">
+        <v>9756</v>
+      </c>
+      <c r="D261">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>19.5</v>
+      </c>
+      <c r="B262">
+        <v>0.151194776748432</v>
+      </c>
+      <c r="C262">
+        <v>9224</v>
+      </c>
+      <c r="D262">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>20</v>
+      </c>
+      <c r="B263">
+        <v>0.150934120454071</v>
+      </c>
+      <c r="C263">
+        <v>8408</v>
+      </c>
+      <c r="D263">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>20.5</v>
+      </c>
+      <c r="B264">
+        <v>0.150663348211758</v>
+      </c>
+      <c r="C264">
+        <v>7452</v>
+      </c>
+      <c r="D264">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>21</v>
+      </c>
+      <c r="B265">
+        <v>0.15049629536542</v>
+      </c>
+      <c r="C265">
+        <v>7040</v>
+      </c>
+      <c r="D265">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>21.5</v>
+      </c>
+      <c r="B266">
+        <v>0.15027488892021</v>
+      </c>
+      <c r="C266">
+        <v>5820</v>
+      </c>
+      <c r="D266">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>22</v>
+      </c>
+      <c r="B267">
+        <v>0.150054060826536</v>
+      </c>
+      <c r="C267">
+        <v>4880</v>
+      </c>
+      <c r="D267">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>22.5</v>
+      </c>
+      <c r="B268">
+        <v>0.149811680723981</v>
+      </c>
+      <c r="C268">
+        <v>3936</v>
+      </c>
+      <c r="D268">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>23</v>
+      </c>
+      <c r="B269">
+        <v>0.14948396342482</v>
+      </c>
+      <c r="C269">
+        <v>2999</v>
+      </c>
+      <c r="D269">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>23.5</v>
+      </c>
+      <c r="B270">
+        <v>0.149224794020347</v>
+      </c>
+      <c r="C270">
+        <v>2180</v>
+      </c>
+      <c r="D270">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>24</v>
+      </c>
+      <c r="B271">
+        <v>0.149013740633741</v>
+      </c>
+      <c r="C271">
+        <v>1620</v>
+      </c>
+      <c r="D271">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>24.5</v>
+      </c>
+      <c r="B272">
+        <v>0.148766473429093</v>
+      </c>
+      <c r="C272">
+        <v>1208</v>
+      </c>
+      <c r="D272">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>25</v>
+      </c>
+      <c r="B273">
+        <v>0.148489245437007</v>
+      </c>
+      <c r="C273">
+        <v>942</v>
+      </c>
+      <c r="D273">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>25.5</v>
+      </c>
+      <c r="B274">
+        <v>0.148278053492716</v>
+      </c>
+      <c r="C274">
+        <v>584</v>
+      </c>
+      <c r="D274">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>26</v>
+      </c>
+      <c r="B275">
+        <v>0.148170605511733</v>
+      </c>
+      <c r="C275">
+        <v>284</v>
+      </c>
+      <c r="D275">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>26.5</v>
+      </c>
+      <c r="B276">
+        <v>0.148252685864766</v>
+      </c>
+      <c r="C276">
+        <v>192</v>
+      </c>
+      <c r="D276">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>27</v>
+      </c>
+      <c r="B277">
+        <v>0.147927797757662</v>
+      </c>
+      <c r="C277">
+        <v>104</v>
+      </c>
+      <c r="D277">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>27.5</v>
+      </c>
+      <c r="B278">
+        <v>0.147961298624674</v>
+      </c>
+      <c r="C278">
+        <v>24</v>
+      </c>
+      <c r="D278">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>28</v>
+      </c>
+      <c r="B279">
+        <v>0.148551940917969</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+      <c r="D279">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>0</v>
+      </c>
+      <c r="B281">
+        <v>0.393997192382812</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>0.5</v>
+      </c>
+      <c r="B282">
+        <v>0.268192291259766</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>1</v>
+      </c>
+      <c r="B283">
+        <v>0.199104309082031</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>1.5</v>
+      </c>
+      <c r="B284">
+        <v>0.171581268310547</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>2</v>
+      </c>
+      <c r="B285">
+        <v>0.17694091796875</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>2.5</v>
+      </c>
+      <c r="B286">
+        <v>0.176822662353516</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>3</v>
+      </c>
+      <c r="B287">
+        <v>0.175235748291016</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>3.5</v>
+      </c>
+      <c r="B288">
+        <v>0.174064636230469</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>4</v>
+      </c>
+      <c r="B289">
+        <v>0.172977447509766</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>4.5</v>
+      </c>
+      <c r="B290">
+        <v>0.171794891357422</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>5</v>
+      </c>
+      <c r="B291">
+        <v>0.171146392822266</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>5.5</v>
+      </c>
+      <c r="B292">
+        <v>0.169921875</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>6</v>
+      </c>
+      <c r="B293">
+        <v>0.168991088867188</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>6.5</v>
+      </c>
+      <c r="B294">
+        <v>0.168670654296875</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>7</v>
+      </c>
+      <c r="B295">
+        <v>0.167686462402344</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>7.5</v>
+      </c>
+      <c r="B296">
+        <v>0.165817260742188</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>8</v>
+      </c>
+      <c r="B297">
+        <v>0.164257049560547</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>8.5</v>
+      </c>
+      <c r="B298">
+        <v>0.163772583007812</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>9</v>
+      </c>
+      <c r="B299">
+        <v>0.163738250732422</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>9.5</v>
+      </c>
+      <c r="B300">
+        <v>0.162792205810547</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>10</v>
+      </c>
+      <c r="B301">
+        <v>0.162113189697266</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>10.5</v>
+      </c>
+      <c r="B302">
+        <v>0.161617279052734</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>11</v>
+      </c>
+      <c r="B303">
+        <v>0.160404205322266</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>11.5</v>
+      </c>
+      <c r="B304">
+        <v>0.158771514892578</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>12</v>
+      </c>
+      <c r="B305">
+        <v>0.158317565917969</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>12.5</v>
+      </c>
+      <c r="B306">
+        <v>0.158317565917969</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>13</v>
+      </c>
+      <c r="B307">
+        <v>0.158584594726562</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>13.5</v>
+      </c>
+      <c r="B308">
+        <v>0.157962799072266</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>14</v>
+      </c>
+      <c r="B309">
+        <v>0.157447814941406</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>14.5</v>
+      </c>
+      <c r="B310">
+        <v>0.156967163085938</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>15</v>
+      </c>
+      <c r="B311">
+        <v>0.156162261962891</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>15.5</v>
+      </c>
+      <c r="B312">
+        <v>0.156192779541016</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>16</v>
+      </c>
+      <c r="B313">
+        <v>0.155982971191406</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>0</v>
+      </c>
+      <c r="B315">
+        <v>0.393997192382812</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>0.5</v>
+      </c>
+      <c r="B316">
+        <v>0.269142150878906</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>1</v>
+      </c>
+      <c r="B317">
+        <v>0.200614929199219</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>1.5</v>
+      </c>
+      <c r="B318">
+        <v>0.173591613769531</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>2</v>
+      </c>
+      <c r="B319">
+        <v>0.179008483886719</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>2.5</v>
+      </c>
+      <c r="B320">
+        <v>0.179660797119141</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>3</v>
+      </c>
+      <c r="B321">
+        <v>0.177501678466797</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>3.5</v>
+      </c>
+      <c r="B322">
+        <v>0.176277160644531</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>4</v>
+      </c>
+      <c r="B323">
+        <v>0.175525665283203</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>4.5</v>
+      </c>
+      <c r="B324">
+        <v>0.174167633056641</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>5</v>
+      </c>
+      <c r="B325">
+        <v>0.173133850097656</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>5.5</v>
+      </c>
+      <c r="B326">
+        <v>0.17138671875</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>6</v>
+      </c>
+      <c r="B327">
+        <v>0.170280456542969</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>6.5</v>
+      </c>
+      <c r="B328">
+        <v>0.169830322265625</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>7</v>
+      </c>
+      <c r="B329">
+        <v>0.168685913085938</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>7.5</v>
+      </c>
+      <c r="B330">
+        <v>0.16754150390625</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>8</v>
+      </c>
+      <c r="B331">
+        <v>0.166919708251953</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>8.5</v>
+      </c>
+      <c r="B332">
+        <v>0.166961669921875</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>9</v>
+      </c>
+      <c r="B333">
+        <v>0.166786193847656</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>9.5</v>
+      </c>
+      <c r="B334">
+        <v>0.165718078613281</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>10</v>
+      </c>
+      <c r="B335">
+        <v>0.164279937744141</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>10.5</v>
+      </c>
+      <c r="B336">
+        <v>0.163276672363281</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>11</v>
+      </c>
+      <c r="B337">
+        <v>0.163337707519531</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>11.5</v>
+      </c>
+      <c r="B338">
+        <v>0.162479400634766</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>12</v>
+      </c>
+      <c r="B339">
+        <v>0.160919189453125</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>12.5</v>
+      </c>
+      <c r="B340">
+        <v>0.159912109375</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>13</v>
+      </c>
+      <c r="B341">
+        <v>0.160770416259766</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>13.5</v>
+      </c>
+      <c r="B342">
+        <v>0.161434173583984</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>14</v>
+      </c>
+      <c r="B343">
+        <v>0.161663055419922</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>14.5</v>
+      </c>
+      <c r="B344">
+        <v>0.160842895507812</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>15</v>
+      </c>
+      <c r="B345">
+        <v>0.160976409912109</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>15.5</v>
+      </c>
+      <c r="B346">
+        <v>0.160717010498047</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>16</v>
+      </c>
+      <c r="B347">
+        <v>0.161148071289062</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>0</v>
+      </c>
+      <c r="B349">
+        <v>0.393997192382812</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>0.5</v>
+      </c>
+      <c r="B350">
+        <v>0.273269653320312</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>1</v>
+      </c>
+      <c r="B351">
+        <v>0.202449798583984</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>1.5</v>
+      </c>
+      <c r="B352">
+        <v>0.173347473144531</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>2</v>
+      </c>
+      <c r="B353">
+        <v>0.173538208007812</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>2.5</v>
+      </c>
+      <c r="B354">
+        <v>0.174968719482422</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>3</v>
+      </c>
+      <c r="B355">
+        <v>0.173542022705078</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>3.5</v>
+      </c>
+      <c r="B356">
+        <v>0.171623229980469</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>4</v>
+      </c>
+      <c r="B357">
+        <v>0.169937133789062</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>4.5</v>
+      </c>
+      <c r="B358">
+        <v>0.169296264648438</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>5</v>
+      </c>
+      <c r="B359">
+        <v>0.168743133544922</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>5.5</v>
+      </c>
+      <c r="B360">
+        <v>0.167881011962891</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>6</v>
+      </c>
+      <c r="B361">
+        <v>0.166278839111328</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>6.5</v>
+      </c>
+      <c r="B362">
+        <v>0.164337158203125</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>7</v>
+      </c>
+      <c r="B363">
+        <v>0.162567138671875</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>7.5</v>
+      </c>
+      <c r="B364">
+        <v>0.162132263183594</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>8</v>
+      </c>
+      <c r="B365">
+        <v>0.161869049072266</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>8.5</v>
+      </c>
+      <c r="B366">
+        <v>0.160816192626953</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>9</v>
+      </c>
+      <c r="B367">
+        <v>0.1593017578125</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>9.5</v>
+      </c>
+      <c r="B368">
+        <v>0.158466339111328</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>10</v>
+      </c>
+      <c r="B369">
+        <v>0.158153533935547</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>10.5</v>
+      </c>
+      <c r="B370">
+        <v>0.15643310546875</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>11</v>
+      </c>
+      <c r="B371">
+        <v>0.155372619628906</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>11.5</v>
+      </c>
+      <c r="B372">
+        <v>0.155178070068359</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>12</v>
+      </c>
+      <c r="B373">
+        <v>0.1551513671875</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>12.5</v>
+      </c>
+      <c r="B374">
+        <v>0.154155731201172</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>13</v>
+      </c>
+      <c r="B375">
+        <v>0.15325927734375</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>13.5</v>
+      </c>
+      <c r="B376">
+        <v>0.152782440185547</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>14</v>
+      </c>
+      <c r="B377">
+        <v>0.152633666992188</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>14.5</v>
+      </c>
+      <c r="B378">
+        <v>0.151386260986328</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>15</v>
+      </c>
+      <c r="B379">
+        <v>0.150558471679688</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>15.5</v>
+      </c>
+      <c r="B380">
+        <v>0.150943756103516</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>16</v>
+      </c>
+      <c r="B381">
+        <v>0.151542663574219</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>